--- a/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
+++ b/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
@@ -672,11 +672,6 @@
           <t>01:38.450</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1357,11 +1352,6 @@
           <t>36670</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6042,11 +6032,6 @@
           <t>04:31.724</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>155751</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14867,11 +14852,6 @@
           <t>04:35.105</t>
         </is>
       </c>
-      <c r="R225" t="inlineStr">
-        <is>
-          <t>155751</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -18894,11 +18874,6 @@
           <t>01:55.814</t>
         </is>
       </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -23806,11 +23781,6 @@
           <t>01:46.783</t>
         </is>
       </c>
-      <c r="R366" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
       <c r="S366" t="inlineStr">
         <is>
           <t>64839</t>
@@ -27000,11 +26970,6 @@
           <t>01:52.909</t>
         </is>
       </c>
-      <c r="R417" t="inlineStr">
-        <is>
-          <t>155751</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -30440,11 +30405,6 @@
           <t>01:57.645</t>
         </is>
       </c>
-      <c r="R471" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -33085,11 +33045,6 @@
           <t>01:47.296</t>
         </is>
       </c>
-      <c r="R513" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
       <c r="S513" t="inlineStr">
         <is>
           <t>64839</t>
@@ -39015,11 +38970,6 @@
           <t>00:37.234</t>
         </is>
       </c>
-      <c r="R607" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -43915,11 +43865,6 @@
           <t>00:44.402</t>
         </is>
       </c>
-      <c r="R686" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -43980,11 +43925,6 @@
           <t>00:44.534</t>
         </is>
       </c>
-      <c r="R687" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -46475,11 +46415,6 @@
           <t>00:34.853</t>
         </is>
       </c>
-      <c r="R726" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -48929,11 +48864,6 @@
           <t>00:45.458</t>
         </is>
       </c>
-      <c r="R765" t="inlineStr">
-        <is>
-          <t>155751</t>
-        </is>
-      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -50674,11 +50604,6 @@
           <t>00:40.797</t>
         </is>
       </c>
-      <c r="R792" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
       <c r="S792" t="inlineStr">
         <is>
           <t>64839</t>
@@ -51819,11 +51744,6 @@
           <t>00:37.687</t>
         </is>
       </c>
-      <c r="R810" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -55594,11 +55514,6 @@
           <t>00:42.958</t>
         </is>
       </c>
-      <c r="R871" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -56794,11 +56709,6 @@
           <t>00:43.464</t>
         </is>
       </c>
-      <c r="R890" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -58019,11 +57929,6 @@
           <t>00:34.314</t>
         </is>
       </c>
-      <c r="R909" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -60569,11 +60474,6 @@
           <t>00:40.553</t>
         </is>
       </c>
-      <c r="R949" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
       <c r="S949" t="inlineStr">
         <is>
           <t>64839</t>
@@ -64167,11 +64067,6 @@
           <t>04:02.621</t>
         </is>
       </c>
-      <c r="R1005" t="inlineStr">
-        <is>
-          <t>155751</t>
-        </is>
-      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -65346,11 +65241,6 @@
           <t>01:37.586</t>
         </is>
       </c>
-      <c r="S1022" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -65418,11 +65308,6 @@
           <t>36670</t>
         </is>
       </c>
-      <c r="T1023" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -70635,11 +70520,6 @@
           <t>22:21.209</t>
         </is>
       </c>
-      <c r="R1102" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
@@ -73958,11 +73838,6 @@
           <t>22:43.520</t>
         </is>
       </c>
-      <c r="R1157" t="inlineStr">
-        <is>
-          <t>155751</t>
-        </is>
-      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -75057,11 +74932,6 @@
           <t>01:51.247</t>
         </is>
       </c>
-      <c r="R1174" t="inlineStr">
-        <is>
-          <t>89175</t>
-        </is>
-      </c>
       <c r="S1174" t="inlineStr">
         <is>
           <t>64839</t>
@@ -81478,11 +81348,6 @@
           <t>00:39.358</t>
         </is>
       </c>
-      <c r="R1272" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -82123,11 +81988,6 @@
           <t>00:46.917</t>
         </is>
       </c>
-      <c r="R1282" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -82386,11 +82246,6 @@
           <t>00:48.333</t>
         </is>
       </c>
-      <c r="R1286" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
@@ -82902,11 +82757,6 @@
           <t>00:36.691</t>
         </is>
       </c>
-      <c r="R1294" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -89844,11 +89694,6 @@
       <c r="P1400" t="inlineStr">
         <is>
           <t>00:42.320</t>
-        </is>
-      </c>
-      <c r="R1400" t="inlineStr">
-        <is>
-          <t>89175</t>
         </is>
       </c>
       <c r="S1400" t="inlineStr">
@@ -90121,7 +89966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90369,17 +90214,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scotty</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BICKNELL</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -90391,61 +90236,61 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>46764</t>
+          <t>126240</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>BLAHOVA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Gergely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BLAHOVA</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gergely</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>BORZOV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -90457,39 +90302,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Yuliya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BORZOV</t>
+          <t>BORZOVA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>52150</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yuliya</t>
+          <t>Jo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BORZOVA</t>
+          <t>BRIGDEN-JONES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -90501,105 +90346,105 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>89175</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lina-Marie</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BIELICKE</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jo</t>
+          <t>Cyrille</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BRIGDEN-JONES</t>
+          <t>CARRE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BROWN</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>52503</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Jiexian Stephenie</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>CHEN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cyrille</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CARRE</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -90611,105 +90456,105 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52503</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jiexian Stephenie</t>
+          <t>Chrisjan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>COETZEE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Valdenice</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>CONCEICAO DO NASCIMENTO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>CSAY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chrisjan</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>COETZEE</t>
+          <t>DAVIDEK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -90721,61 +90566,61 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Valdenice</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CONCEICAO DO NASCIMENTO</t>
+          <t>DE CESARE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>41545</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Rudolf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CSAY</t>
+          <t>DOMBI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Miklos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DAVIDEK</t>
+          <t>DUDAS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -90787,17 +90632,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>65549</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Kristian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE CESARE</t>
+          <t>DUSHEV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -90809,17 +90654,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>41545</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rudolf</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DOMBI</t>
+          <t>DVORAK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -90831,17 +90676,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Miklos</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DUDAS</t>
+          <t>EGAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -90853,39 +90698,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kristian</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DUSHEV</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DVORAK</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -90897,61 +90742,61 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Ariel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EGAN</t>
+          <t>FARRAR-WELLMAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>FITZGERALD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>FLORCZAK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -90963,17 +90808,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FARRAR-WELLMAN</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -90985,17 +90830,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FITZGERALD</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -91007,17 +90852,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FLORCZAK</t>
+          <t>GELLE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -91029,61 +90874,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GOBLE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GELLE</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -91095,17 +90940,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>75776</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GOBLE</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -91117,17 +90962,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>GUYOT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -91139,17 +90984,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Lubomir</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>HAGARA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -91161,17 +91006,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>HALL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -91183,17 +91028,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Verena</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GUYOT</t>
+          <t>HANTL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -91205,17 +91050,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lubomir</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HAGARA</t>
+          <t>HARAZHA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -91227,39 +91072,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HALL</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verena</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HANTL</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -91271,17 +91116,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HARAZHA</t>
+          <t>HAVEL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -91293,61 +91138,61 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HEATH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Mirziyodjon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>KHOJIEV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HAVEL</t>
+          <t>HORNSBY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -91359,17 +91204,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HEATH</t>
+          <t>HUBERT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -91381,17 +91226,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mirziyodjon</t>
+          <t>Tibor</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KHOJIEV</t>
+          <t>HUFNAGEL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -91403,17 +91248,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HORNSBY</t>
+          <t>HYBOIS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -91425,39 +91270,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Belen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HUBERT</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tibor</t>
+          <t>Vilyam</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HUFNAGEL</t>
+          <t>IBRAGIMOV</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -91469,17 +91314,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HYBOIS</t>
+          <t>JAKUBIK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -91491,17 +91336,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Belen</t>
+          <t>Natasa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>DOUCHEV-JANIC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -91513,17 +91358,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vilyam</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IBRAGIMOV</t>
+          <t>JANKOVEC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -91535,17 +91380,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gabor</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JAKUBIK</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -91557,17 +91402,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Natasa</t>
+          <t>Shiho</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DOUCHEV-JANIC</t>
+          <t>KAKIZAKI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -91579,17 +91424,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>41546</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Zoltan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JANKOVEC</t>
+          <t>KAMMERER</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -91601,83 +91446,83 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KAZAKOVA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shiho</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KAKIZAKI</t>
+          <t>KIRCHEV</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>41546</t>
+          <t>64839</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zoltan</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KAMMERER</t>
+          <t>KLEIN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KAZAKOVA</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -91689,17 +91534,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KIRCHEV</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -91711,83 +91556,83 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>64839</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Rastislav</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KLEIN</t>
+          <t>KOHUT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>42055</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Artsem</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KOZYR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Danuta</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KOZAK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rastislav</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOHUT</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -91799,17 +91644,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Artsem</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KOZYR</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -91821,39 +91666,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t>Kurt</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOZAK</t>
+          <t>KUSCHELA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>KUSOVSKY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -91865,17 +91710,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>KOKENY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -91887,17 +91732,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>49666</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kurt</t>
+          <t>Marton</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KUSCHELA</t>
+          <t>KOVER</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -91909,17 +91754,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KUSOVSKY</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -91931,17 +91776,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KOKENY</t>
+          <t>LECRUBIER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -91953,127 +91798,127 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>49666</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marton</t>
+          <t>Sun Ja</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KOVER</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Wei Ling Geraldine</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LECRUBIER</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sun Ja</t>
+          <t>Tony Gill</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>LESPOIR</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wei Ling Geraldine</t>
+          <t>Guiqiang</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Zhangli</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -92085,17 +91930,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tony Gill</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LESPOIR</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -92107,61 +91952,61 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Guiqiang</t>
+          <t>Una Helen Bean</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LOUNDER</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zhangli</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LOUW</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>53067</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>MAEHLER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -92173,17 +92018,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>155751</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Van Danh</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TRAN</t>
+          <t>MAKHLAI</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -92195,17 +92040,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Una Helen Bean</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LOUNDER</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -92217,17 +92062,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Momotaro</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LOUW</t>
+          <t>MATSUSHITA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -92239,61 +92084,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jaimee</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LOVETT</t>
+          <t>MCKEEVER</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>53067</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Erika</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MAEHLER</t>
+          <t>MEDVECZKY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>52285</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MAKHLAI</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -92305,39 +92150,39 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MIKE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Momotaro</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MATSUSHITA</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -92349,17 +92194,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MCKEEVER</t>
+          <t>MISKOVSKY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -92371,39 +92216,39 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Erika</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MEDVECZKY</t>
+          <t>MITTELSTEDT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Keiji</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MIZUMOTO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -92415,39 +92260,39 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Nikolina</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MIKE</t>
+          <t>MOLDOVAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>MOLNAR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -92459,17 +92304,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MISKOVSKY</t>
+          <t>MORTIMER</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -92481,17 +92326,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MITTELSTEDT</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -92503,39 +92348,39 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Keiji</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MIZUMOTO</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>99701</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nikolina</t>
+          <t>Daniela</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MOLDOVAN</t>
+          <t>NEDEVA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -92547,61 +92392,61 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>53045</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Xiang Ru Annabelle</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MOLNAR</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Asumi</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MORTIMER</t>
+          <t>OHMURA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -92613,61 +92458,61 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>42769</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Celso</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>DIAS DE OLIVEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>99701</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Daniela</t>
+          <t>Ronilson Matias De</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NEDEVA</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>53045</t>
+          <t>84923</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Xiang Ru Annabelle</t>
+          <t>Yuka</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>ONO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -92679,17 +92524,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Asumi</t>
+          <t>Genevieve Wendy Susan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>OHMURA</t>
+          <t>ORTON</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -92701,17 +92546,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Dejan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>PAJIC</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -92723,39 +92568,39 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Celso</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DIAS DE OLIVEIRA JUNIOR</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ronilson Matias De</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -92767,39 +92612,39 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>84923</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Yuka</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ONO</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Genevieve Wendy Susan</t>
+          <t>Ariela Cesar</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ORTON</t>
+          <t>PINTO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -92811,39 +92656,39 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dejan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PAJIC</t>
+          <t>PIPITSOULI</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Spela</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PONOMARENKO JANIC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -92855,39 +92700,39 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>PORTELA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PUTTO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -92899,83 +92744,83 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ariela Cesar</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PINTO</t>
+          <t>RABCHANKA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Brady Daniel Heim</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PIPITSOULI</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Spela</t>
+          <t>Kristian</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PONOMARENKO JANIC</t>
+          <t>REEVES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Wenjun</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PORTELA</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -92987,17 +92832,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Gilvan</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PUTTO</t>
+          <t>BITTENCOURT RIBEIRO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -93009,39 +92854,39 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>RABCHANKA</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Brady Daniel Heim</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -93053,17 +92898,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Kristian</t>
+          <t>Benjamin Rolph Mathew</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>REEVES</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -93075,17 +92920,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Wenjun</t>
+          <t>Aliz</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -93097,17 +92942,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gilvan</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BITTENCOURT RIBEIRO</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -93119,39 +92964,39 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>SCHMUDE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>SCHOFIELD</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -93163,39 +93008,39 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Benjamin Rolph Mathew</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>56596</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Aliz</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -93207,193 +93052,193 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pal</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SEAH</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SCHMUDE</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SCHOFIELD</t>
+          <t>SHUBINA</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Edson Isaias</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>FREITAS DA SILVA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Emanuel</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>52506</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SEAH</t>
+          <t>SIMART</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>Erlon</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SHUBINA</t>
+          <t>DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Edson Isaias</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FREITAS DA SILVA</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -93405,17 +93250,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Emanuel</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -93427,17 +93272,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Kostja</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SIMART</t>
+          <t>STROINSKI</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -93449,17 +93294,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>STYAN</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -93471,17 +93316,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Erlon</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DE SOUZA SILVA</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -93493,39 +93338,39 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Gabriella</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>STERBA</t>
+          <t>SZABO</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Tamas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>SZALAI</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -93537,17 +93382,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Kostja</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>STROINSKI</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -93559,17 +93404,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>98550</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Matyas</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>STYAN</t>
+          <t>SAFRAN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -93581,17 +93426,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Juraj</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SVAB</t>
+          <t>TARR</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -93603,39 +93448,39 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Gabriella</t>
+          <t>Zi Qiang</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SZABO</t>
+          <t>TAY</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tamas</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SZALAI</t>
+          <t>TREFIL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -93647,61 +93492,61 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>TROEL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>98550</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Matyas</t>
+          <t>Dzsenifer</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SAFRAN</t>
+          <t>TOTH</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Juraj</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TARR</t>
+          <t>TOTH</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -93713,39 +93558,39 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Zi Qiang</t>
+          <t>Ninetta</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TAY</t>
+          <t>VAD</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TREFIL</t>
+          <t>VAITSISHKIN</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -93757,61 +93602,61 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Attila</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TROEL</t>
+          <t>VAJDA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dzsenifer</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TOTH</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TOTH</t>
+          <t>VANDREY</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -93823,61 +93668,61 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ninetta</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VAD</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>VAITSISHKIN</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>41550</t>
+          <t>45225</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Attila</t>
+          <t>Andras</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>VAJDA</t>
+          <t>VASS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -93889,17 +93734,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VAUCHETSKI</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -93911,149 +93756,149 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Hannah Marie</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>VANDREY</t>
+          <t>VAUGHAN</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VINCENT-LAPOINTE</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>VLCEK</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>45225</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Andras</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>VASS</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>60075</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Aliaksandr</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>VAUCHETSKI</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Hannah Marie</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>VAUGHAN</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>VINCENT-LAPOINTE</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -94065,17 +93910,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>52586</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Keat Howe Luke</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>VLCEK</t>
+          <t>YAP</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -94087,240 +93932,108 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>60075</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Feng</t>
+          <t>Peng</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Yubo</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>52586</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Keat Howe Luke</t>
+          <t>Milenko</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>YAP</t>
+          <t>ZORIC</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>36310</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Jost</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>ZAKRAJSEK</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Hong</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>ZHANG</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>60015</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Peng</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>52182</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>61025</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Yubo</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>42179</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Milenko</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>ZORIC</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
+++ b/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
@@ -1012,6 +1012,11 @@
           <t>55512</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1207,6 +1212,11 @@
           <t>36458</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>36457</t>
@@ -2207,6 +2217,11 @@
           <t>04:20.425</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4027,6 +4042,11 @@
           <t>03:36.046</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4087,6 +4107,11 @@
           <t>03:36.214</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5587,6 +5612,11 @@
           <t>03:57.074</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6857,6 +6887,11 @@
           <t>69073</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6917,6 +6952,11 @@
           <t>03:54.629</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10092,6 +10132,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10362,6 +10407,11 @@
           <t>42468</t>
         </is>
       </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10972,6 +11022,11 @@
           <t>52573</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11302,6 +11357,11 @@
           <t>55512</t>
         </is>
       </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12647,6 +12707,11 @@
           <t>04:19.031</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12767,6 +12832,11 @@
           <t>03:36.879</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13902,6 +13972,11 @@
           <t>03:36.227</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14657,6 +14732,11 @@
           <t>03:54.509</t>
         </is>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -18024,6 +18104,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18559,6 +18644,11 @@
           <t>42468</t>
         </is>
       </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18624,6 +18714,11 @@
           <t>52573</t>
         </is>
       </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -21371,6 +21466,11 @@
           <t>01:57.378</t>
         </is>
       </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -23401,6 +23501,11 @@
           <t>01:52.978</t>
         </is>
       </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -24596,6 +24701,11 @@
           <t>01:41.733</t>
         </is>
       </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -24716,6 +24826,11 @@
           <t>01:44.487</t>
         </is>
       </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -25708,6 +25823,11 @@
           <t>01:43.230</t>
         </is>
       </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -26023,6 +26143,11 @@
           <t>01:59.628</t>
         </is>
       </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -26790,6 +26915,11 @@
           <t>01:45.643</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -27030,6 +27160,11 @@
           <t>01:53.605</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -28900,6 +29035,11 @@
           <t>69073</t>
         </is>
       </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -31910,6 +32050,11 @@
           <t>01:56.793</t>
         </is>
       </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -33875,6 +34020,11 @@
           <t>01:57.326</t>
         </is>
       </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -33995,6 +34145,11 @@
           <t>01:40.102</t>
         </is>
       </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -34490,6 +34645,11 @@
           <t>01:40.934</t>
         </is>
       </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -34870,6 +35030,11 @@
           <t>01:57.110</t>
         </is>
       </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -35755,6 +35920,11 @@
           <t>01:43.020</t>
         </is>
       </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -36445,6 +36615,11 @@
           <t>01:46.654</t>
         </is>
       </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -38165,6 +38340,11 @@
           <t>69073</t>
         </is>
       </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -39525,6 +39705,11 @@
           <t>00:38.143</t>
         </is>
       </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -45965,6 +46150,11 @@
           <t>69073</t>
         </is>
       </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -46920,6 +47110,11 @@
           <t>00:39.105</t>
         </is>
       </c>
+      <c r="S734" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -48619,6 +48814,11 @@
           <t>42447</t>
         </is>
       </c>
+      <c r="S761" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -48804,6 +49004,11 @@
           <t>00:41.756</t>
         </is>
       </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -50154,6 +50359,11 @@
           <t>00:42.670</t>
         </is>
       </c>
+      <c r="S785" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -52794,6 +53004,11 @@
           <t>00:37.719</t>
         </is>
       </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -57419,6 +57634,11 @@
           <t>69073</t>
         </is>
       </c>
+      <c r="S901" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -58059,6 +58279,11 @@
           <t>00:38.412</t>
         </is>
       </c>
+      <c r="S911" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -59959,6 +60184,11 @@
           <t>42447</t>
         </is>
       </c>
+      <c r="S941" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -60144,6 +60374,11 @@
           <t>00:41.431</t>
         </is>
       </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -60604,6 +60839,11 @@
           <t>00:41.453</t>
         </is>
       </c>
+      <c r="S951" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -62849,6 +63089,11 @@
           <t>04:10.945</t>
         </is>
       </c>
+      <c r="R986" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -64005,6 +64250,11 @@
           <t>03:54.665</t>
         </is>
       </c>
+      <c r="R1004" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -64134,6 +64384,11 @@
           <t>42468</t>
         </is>
       </c>
+      <c r="T1006" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
@@ -64474,6 +64729,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T1011" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -64675,6 +64935,11 @@
           <t>52573</t>
         </is>
       </c>
+      <c r="U1014" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -64896,6 +65161,11 @@
           <t>36458</t>
         </is>
       </c>
+      <c r="T1017" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
       <c r="U1017" t="inlineStr">
         <is>
           <t>36457</t>
@@ -65963,6 +66233,11 @@
           <t>03:27.356</t>
         </is>
       </c>
+      <c r="R1033" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -66092,6 +66367,11 @@
           <t>03:28.724</t>
         </is>
       </c>
+      <c r="R1035" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -68992,6 +69272,11 @@
           <t>47429</t>
         </is>
       </c>
+      <c r="T1079" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
       <c r="U1079" t="inlineStr">
         <is>
           <t>47436</t>
@@ -70097,6 +70382,11 @@
           <t>21:26.471</t>
         </is>
       </c>
+      <c r="R1095" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -71066,6 +71356,11 @@
           <t>23:18.971</t>
         </is>
       </c>
+      <c r="R1111" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
@@ -71477,6 +71772,11 @@
       <c r="N1118" t="n">
         <v>26</v>
       </c>
+      <c r="R1118" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="X1118" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -73361,6 +73661,11 @@
           <t>21:31.034</t>
         </is>
       </c>
+      <c r="R1149" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
@@ -77309,6 +77614,11 @@
           <t>01:43.030</t>
         </is>
       </c>
+      <c r="R1210" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
@@ -77634,6 +77944,11 @@
           <t>01:49.408</t>
         </is>
       </c>
+      <c r="R1215" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
@@ -79227,6 +79542,11 @@
           <t>02:02.709</t>
         </is>
       </c>
+      <c r="R1239" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -79939,6 +80259,11 @@
           <t>01:49.086</t>
         </is>
       </c>
+      <c r="R1250" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
@@ -81663,6 +81988,11 @@
           <t>00:40.246</t>
         </is>
       </c>
+      <c r="R1277" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
@@ -89632,6 +89962,11 @@
       <c r="P1399" t="inlineStr">
         <is>
           <t>00:41.756</t>
+        </is>
+      </c>
+      <c r="S1399" t="inlineStr">
+        <is>
+          <t>70017</t>
         </is>
       </c>
     </row>
@@ -89966,7 +90301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94039,6 +94374,270 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Dongjin</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SHIN</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>MEHAK</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tamas</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KISS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Antoine</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>MEUNIER</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Aleksey</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>MOCHALOV</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Vyacheslav</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>GORN</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Gukjoo</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>KIM</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>103885</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Wei Liang Bill</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
+++ b/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
@@ -672,6 +672,11 @@
           <t>01:38.450</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18969,6 +18974,11 @@
           <t>01:55.814</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -30545,6 +30555,11 @@
           <t>01:57.645</t>
         </is>
       </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -39150,6 +39165,11 @@
           <t>00:37.234</t>
         </is>
       </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -44050,6 +44070,11 @@
           <t>00:44.402</t>
         </is>
       </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -44110,6 +44135,11 @@
           <t>00:44.534</t>
         </is>
       </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -46605,6 +46635,11 @@
           <t>00:34.853</t>
         </is>
       </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -51954,6 +51989,11 @@
           <t>00:37.687</t>
         </is>
       </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -55729,6 +55769,11 @@
           <t>00:42.958</t>
         </is>
       </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -56924,6 +56969,11 @@
           <t>00:43.464</t>
         </is>
       </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -58149,6 +58199,11 @@
           <t>00:34.314</t>
         </is>
       </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -65511,6 +65566,11 @@
           <t>01:37.586</t>
         </is>
       </c>
+      <c r="S1022" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -70810,6 +70870,11 @@
           <t>22:21.209</t>
         </is>
       </c>
+      <c r="R1102" t="inlineStr">
+        <is>
+          <t>119523</t>
+        </is>
+      </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
@@ -81673,6 +81738,11 @@
           <t>00:39.358</t>
         </is>
       </c>
+      <c r="R1272" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -82318,6 +82388,11 @@
           <t>00:46.917</t>
         </is>
       </c>
+      <c r="R1282" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -82576,6 +82651,11 @@
           <t>00:48.333</t>
         </is>
       </c>
+      <c r="R1286" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
@@ -83085,6 +83165,11 @@
       <c r="P1294" t="inlineStr">
         <is>
           <t>00:36.691</t>
+        </is>
+      </c>
+      <c r="R1294" t="inlineStr">
+        <is>
+          <t>51822</t>
         </is>
       </c>
     </row>
@@ -90301,7 +90386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94638,6 +94723,94 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Scotty</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BICKNELL</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Jaimee</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>LOVETT</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>119523</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>BROWN</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ZHANG</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
+++ b/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
@@ -672,11 +672,6 @@
           <t>01:38.450</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18974,11 +18969,6 @@
           <t>01:55.814</t>
         </is>
       </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -30555,11 +30545,6 @@
           <t>01:57.645</t>
         </is>
       </c>
-      <c r="R471" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -39165,11 +39150,6 @@
           <t>00:37.234</t>
         </is>
       </c>
-      <c r="R607" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -44070,11 +44050,6 @@
           <t>00:44.402</t>
         </is>
       </c>
-      <c r="R686" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -44135,11 +44110,6 @@
           <t>00:44.534</t>
         </is>
       </c>
-      <c r="R687" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -46635,11 +46605,6 @@
           <t>00:34.853</t>
         </is>
       </c>
-      <c r="R726" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -51989,11 +51954,6 @@
           <t>00:37.687</t>
         </is>
       </c>
-      <c r="R810" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -55769,11 +55729,6 @@
           <t>00:42.958</t>
         </is>
       </c>
-      <c r="R871" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -56969,11 +56924,6 @@
           <t>00:43.464</t>
         </is>
       </c>
-      <c r="R890" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -58199,11 +58149,6 @@
           <t>00:34.314</t>
         </is>
       </c>
-      <c r="R909" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -65566,11 +65511,6 @@
           <t>01:37.586</t>
         </is>
       </c>
-      <c r="S1022" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -70870,11 +70810,6 @@
           <t>22:21.209</t>
         </is>
       </c>
-      <c r="R1102" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
@@ -81738,11 +81673,6 @@
           <t>00:39.358</t>
         </is>
       </c>
-      <c r="R1272" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -82388,11 +82318,6 @@
           <t>00:46.917</t>
         </is>
       </c>
-      <c r="R1282" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -82651,11 +82576,6 @@
           <t>00:48.333</t>
         </is>
       </c>
-      <c r="R1286" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
@@ -83165,11 +83085,6 @@
       <c r="P1294" t="inlineStr">
         <is>
           <t>00:36.691</t>
-        </is>
-      </c>
-      <c r="R1294" t="inlineStr">
-        <is>
-          <t>51822</t>
         </is>
       </c>
     </row>
@@ -90386,7 +90301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94723,94 +94638,6 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Scotty</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>BICKNELL</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>51823</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Jaimee</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>LOVETT</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>BROWN</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Hong</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>ZHANG</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
+++ b/events/Szeged_2010_WC/Szeged_2010_WC_Results.xlsx
@@ -22141,6 +22141,11 @@
           <t>01:52.841</t>
         </is>
       </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -32175,6 +32180,11 @@
           <t>01:58.599</t>
         </is>
       </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -42440,6 +42450,11 @@
           <t>00:42.499</t>
         </is>
       </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -53444,6 +53459,11 @@
           <t>00:41.428</t>
         </is>
       </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -83921,6 +83941,11 @@
       <c r="P1307" t="inlineStr">
         <is>
           <t>00:44.732</t>
+        </is>
+      </c>
+      <c r="R1307" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -90301,7 +90326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94638,6 +94663,28 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
